--- a/11thModule/Data_Science/Atividade_II_Naive_Tarefa/Summary.xlsx
+++ b/11thModule/Data_Science/Atividade_II_Naive_Tarefa/Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code Suff\SI.Uniuv\11thModule\Data_Science\Atividade_II_Naive_Tarefa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BAB53E-3974-4184-BB25-5B869A4F7627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA79E03-5E03-4E9C-BD6E-DBFB3E93FA91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C6C40137-2771-4AFB-8933-016CFAC2BED0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="91">
   <si>
     <t>Dataset:</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>Original Shape:</t>
+  </si>
+  <si>
+    <t>K-Means</t>
   </si>
 </sst>
 </file>
@@ -400,7 +403,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -438,32 +441,35 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -818,189 +824,189 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="5"/>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="14"/>
       <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="20"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="15"/>
       <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="13"/>
       <c r="K3" s="5"/>
     </row>
     <row r="4" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="13"/>
       <c r="K4" s="5"/>
     </row>
     <row r="5" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="13"/>
       <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
       <c r="K6" s="5"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
       <c r="K8" s="5"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
       <c r="K9" s="5"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
       <c r="K11" s="5"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
       <c r="K12" s="5"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
       <c r="K13" s="5"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1020,10 +1026,10 @@
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E15" s="13"/>
+      <c r="E15" s="19"/>
       <c r="F15" s="11" t="s">
         <v>6</v>
       </c>
@@ -1048,12 +1054,12 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="1" t="s">
         <v>38</v>
       </c>
@@ -1073,12 +1079,12 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
       <c r="F18" s="11" t="s">
         <v>57</v>
       </c>
@@ -1098,12 +1104,12 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
       <c r="F19" s="11" t="s">
         <v>59</v>
       </c>
@@ -1123,12 +1129,12 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
       <c r="F20" s="11" t="s">
         <v>60</v>
       </c>
@@ -1148,12 +1154,12 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
       <c r="F21" s="11" t="s">
         <v>62</v>
       </c>
@@ -1173,12 +1179,12 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
       <c r="F22" s="11" t="s">
         <v>64</v>
       </c>
@@ -1198,12 +1204,12 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
       <c r="F23" s="11" t="s">
         <v>66</v>
       </c>
@@ -1223,12 +1229,12 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
       <c r="F24" s="11" t="s">
         <v>68</v>
       </c>
@@ -1248,12 +1254,12 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
       <c r="F25" s="11" t="s">
         <v>70</v>
       </c>
@@ -1273,12 +1279,12 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
       <c r="F26" s="2" t="s">
         <v>72</v>
       </c>
@@ -1298,12 +1304,12 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
       <c r="F27" s="2" t="s">
         <v>73</v>
       </c>
@@ -1323,12 +1329,12 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
       <c r="F28" s="2" t="s">
         <v>57</v>
       </c>
@@ -1348,12 +1354,12 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
       <c r="F29" s="2" t="s">
         <v>59</v>
       </c>
@@ -1373,12 +1379,12 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
       <c r="F30" s="2" t="s">
         <v>60</v>
       </c>
@@ -1398,12 +1404,12 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
       <c r="F31" s="2" t="s">
         <v>62</v>
       </c>
@@ -1423,12 +1429,12 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
       <c r="F32" s="2" t="s">
         <v>64</v>
       </c>
@@ -1448,12 +1454,12 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
       <c r="F33" s="2" t="s">
         <v>66</v>
       </c>
@@ -1473,12 +1479,12 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
       <c r="F34" s="2" t="s">
         <v>74</v>
       </c>
@@ -1498,12 +1504,12 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
       <c r="F35" s="2" t="s">
         <v>75</v>
       </c>
@@ -1523,53 +1529,53 @@
     </row>
     <row r="36" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
       <c r="J36" s="9"/>
       <c r="K36" s="5"/>
     </row>
     <row r="37" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
       <c r="J37" s="9"/>
       <c r="K37" s="5"/>
     </row>
     <row r="38" spans="1:11" ht="21" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
       <c r="J38" s="9"/>
       <c r="K38" s="5"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
       <c r="F39" s="2" t="s">
         <v>16</v>
       </c>
@@ -1579,297 +1585,408 @@
       <c r="H39" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I39" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="K39" s="5"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
       <c r="F40" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>42</v>
       </c>
+      <c r="H40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="K40" s="5"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
       <c r="F41" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>42</v>
       </c>
+      <c r="H41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="K41" s="5"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
       <c r="F42" s="4">
         <v>0.106538238234413</v>
       </c>
       <c r="G42" s="4">
         <v>0.70527400544596297</v>
       </c>
+      <c r="H42" s="22">
+        <v>0.30680000000000002</v>
+      </c>
+      <c r="I42" s="22">
+        <v>0</v>
+      </c>
       <c r="K42" s="5"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
       <c r="F43" s="4">
         <v>0.105802823568277</v>
       </c>
       <c r="G43" s="4">
         <v>0.66865439825058504</v>
       </c>
+      <c r="H43" s="22">
+        <v>0.28449999999999998</v>
+      </c>
+      <c r="I43" s="22">
+        <v>0</v>
+      </c>
       <c r="K43" s="5"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
       <c r="F44" s="4">
         <v>0.107804777224146</v>
       </c>
       <c r="G44" s="4">
         <v>0.70862629483628503</v>
       </c>
+      <c r="H44" s="22">
+        <v>0.32079999999999997</v>
+      </c>
+      <c r="I44" s="22">
+        <v>0</v>
+      </c>
       <c r="K44" s="5"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
       <c r="F45" s="4">
         <v>0.107298361668877</v>
       </c>
       <c r="G45" s="4">
         <v>0.67220575067617805</v>
       </c>
+      <c r="H45" s="22">
+        <v>0.1799</v>
+      </c>
+      <c r="I45" s="22">
+        <v>0</v>
+      </c>
       <c r="K45" s="5"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
       <c r="F46" s="4">
         <v>5.8778613256321097E-2</v>
       </c>
       <c r="G46" s="4">
         <v>0.69385039311138597</v>
       </c>
+      <c r="H46" s="22">
+        <v>5.74E-2</v>
+      </c>
+      <c r="I46" s="22">
+        <v>0</v>
+      </c>
       <c r="K46" s="5"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
       <c r="F47" s="4">
         <v>5.8778613256321097E-2</v>
       </c>
       <c r="G47" s="4">
         <v>0.69385039311138597</v>
       </c>
+      <c r="H47" s="22">
+        <v>5.6599999999999998E-2</v>
+      </c>
+      <c r="I47" s="22">
+        <v>0</v>
+      </c>
       <c r="K47" s="5"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
       <c r="F48" s="4">
         <v>5.9996511526139502E-2</v>
       </c>
       <c r="G48" s="4">
         <v>0.697307711746049</v>
       </c>
+      <c r="H48" s="22">
+        <v>5.5500000000000001E-2</v>
+      </c>
+      <c r="I48" s="22">
+        <v>0</v>
+      </c>
       <c r="K48" s="5"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
       <c r="F49" s="4">
         <v>6.0190658039576302E-2</v>
       </c>
       <c r="G49" s="4">
         <v>0.69724299624157005</v>
       </c>
+      <c r="H49" s="22">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="I49" s="22">
+        <v>0</v>
+      </c>
       <c r="K49" s="5"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
       <c r="F50" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>42</v>
       </c>
+      <c r="H50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="K50" s="5"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
       <c r="F51" s="4" t="s">
         <v>42</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>42</v>
       </c>
+      <c r="H51" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="K51" s="5"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
       <c r="F52" s="4">
         <v>0.106525418401144</v>
       </c>
       <c r="G52" s="4">
         <v>0.60883434433332495</v>
       </c>
+      <c r="H52" s="22">
+        <v>0.29680000000000001</v>
+      </c>
+      <c r="I52" s="22">
+        <v>0</v>
+      </c>
       <c r="K52" s="5"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
-      <c r="B53" s="15" t="s">
+      <c r="B53" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
       <c r="F53" s="4">
         <v>0.10596011306106801</v>
       </c>
       <c r="G53" s="4">
         <v>0.54933626545930103</v>
       </c>
+      <c r="H53" s="22">
+        <v>0.3574</v>
+      </c>
+      <c r="I53" s="22">
+        <v>0</v>
+      </c>
       <c r="K53" s="5"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
       <c r="F54" s="4">
         <v>0.108197849082001</v>
       </c>
       <c r="G54" s="4">
         <v>0.61108843114198497</v>
       </c>
+      <c r="H54" s="22">
+        <v>0.34739999999999999</v>
+      </c>
+      <c r="I54" s="22">
+        <v>0</v>
+      </c>
       <c r="K54" s="5"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
-      <c r="B55" s="15" t="s">
+      <c r="B55" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
       <c r="F55" s="4">
         <v>0.106962103904163</v>
       </c>
       <c r="G55" s="4">
         <v>0.55183755356537301</v>
       </c>
+      <c r="H55" s="22">
+        <v>0.36509999999999998</v>
+      </c>
+      <c r="I55" s="22">
+        <v>0</v>
+      </c>
       <c r="K55" s="5"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
-      <c r="B56" s="15" t="s">
+      <c r="B56" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
       <c r="F56" s="4">
         <v>5.9249673591591501E-2</v>
       </c>
       <c r="G56" s="4">
         <v>0.69534486819784302</v>
       </c>
+      <c r="H56" s="22">
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="I56" s="22">
+        <v>0</v>
+      </c>
       <c r="K56" s="5"/>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
       <c r="F57" s="4">
         <v>5.8857648933223303E-2</v>
       </c>
       <c r="G57" s="4">
         <v>0.69536244439888395</v>
       </c>
+      <c r="H57" s="22">
+        <v>0.29310000000000003</v>
+      </c>
+      <c r="I57" s="22">
+        <v>0</v>
+      </c>
       <c r="K57" s="5"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -1882,7 +1999,7 @@
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -1895,7 +2012,7 @@
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -1914,6 +2031,41 @@
   </sortState>
   <dataConsolidate/>
   <mergeCells count="51">
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B36:I38"/>
+    <mergeCell ref="B3:I5"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B17:E17"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="B22:E22"/>
@@ -1930,41 +2082,6 @@
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B36:I38"/>
-    <mergeCell ref="B3:I5"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="B9:I9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{94966182-C9A1-45DE-8E1F-4634D642516C}"/>
